--- a/BWI/bestwine_output/bestwine_Kenya.xlsx
+++ b/BWI/bestwine_output/bestwine_Kenya.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA56"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6220,6 +6220,83 @@
       <c r="Z56" s="2" t="inlineStr"/>
       <c r="AA56" s="2" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Monty's Kenya Limited</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Monty's Kenya Limited</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>105381</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi County</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>P O Box 430</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>00606</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montyskenya.com</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>sales@montyskenya.com</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MontysKenyaLimited/</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montyskenyaltd/</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Kenya.xlsx
+++ b/BWI/bestwine_output/bestwine_Kenya.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA57"/>
+  <dimension ref="A1:AA59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6297,6 +6297,176 @@
       <c r="Z57" s="2" t="inlineStr"/>
       <c r="AA57" s="2" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Viva Global Ltd</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Viva Global Ltd</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>50162</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi County</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Eden Square, Block 1, 6th Floor, Westlands Road</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://viva.global</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>info@viva-global.net</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>+254 20 3660000</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>C.75628</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vivagloballtd/</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viva_global/</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Monty's Kenya Limited</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Monty's Kenya Limited</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>105381</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi County</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>P O Box 430</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>00606</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montyskenya.com</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>sales@montyskenya.com</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MontysKenyaLimited/</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montyskenyaltd/</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
